--- a/research/runs/20260228-180047-excel-compat-empirical-pass-01/fixtures/coercion_wave1/SCN-EB024-OP-CORE.xlsx
+++ b/research/runs/20260228-180047-excel-compat-empirical-pass-01/fixtures/coercion_wave1/SCN-EB024-OP-CORE.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Work\DnaCalc\Foundation\research\runs\20260228-180047-excel-compat-empirical-pass-01\fixtures\coercion_wave1\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{ADFF0463-6BAF-412C-A441-DDF5B2E07BEE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{28163079-1623-4549-9483-300FECF98F55}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="7440" yWindow="3075" windowWidth="17460" windowHeight="11595" xr2:uid="{6B6F6640-D77E-4217-9A71-CA7390938798}"/>
+    <workbookView xWindow="3135" yWindow="3885" windowWidth="11955" windowHeight="11595" xr2:uid="{DAE0CFF3-A045-47AF-BB0C-E79013396142}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -402,7 +402,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B00D2711-A4A6-4CBC-B924-0EF00DD9EC73}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3FF761C6-A269-4987-805D-D701581A2CA9}">
   <dimension ref="B1:B10"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
@@ -451,13 +451,13 @@
     <row r="8" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B8" s="1">
         <f ca="1">TODAY()+1</f>
-        <v>46082</v>
+        <v>46083</v>
       </c>
     </row>
     <row r="9" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B9" s="1">
         <f ca="1">TODAY()</f>
-        <v>46081</v>
+        <v>46082</v>
       </c>
     </row>
     <row r="10" spans="2:2" x14ac:dyDescent="0.25">
